--- a/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
+++ b/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="19">
   <si>
     <t>a</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>3=</t>
   </si>
 </sst>
 </file>
@@ -468,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871B0360-4A65-8D4C-9F92-BAB28DCD4F5A}">
-  <dimension ref="B9:F17"/>
+  <dimension ref="B9:F18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
@@ -494,15 +497,9 @@
       <c r="C11" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>17</v>
-      </c>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="0" t="s">
@@ -516,37 +513,33 @@
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C14" s="0" t="n">
         <v>10.0</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D14" s="0" t="n">
         <v>20.0</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E14" s="0" t="n">
         <v>30.0</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F14" s="0" t="n">
         <v>40.0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B14" s="0" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E14" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.2">
@@ -597,6 +590,23 @@
         <v>0.0</v>
       </c>
       <c r="F17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F18" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>

--- a/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
+++ b/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>a</t>
   </si>
@@ -65,37 +65,19 @@
     <t>HC1</t>
   </si>
   <si>
-    <t>b</t>
-  </si>
-  <si>
     <t>a1</t>
   </si>
   <si>
-    <t>b1</t>
+    <t>Integer a1</t>
   </si>
   <si>
     <t>Integer b1</t>
   </si>
   <si>
-    <t>Integer a1</t>
-  </si>
-  <si>
-    <t>a1==a</t>
+    <t>a1 ==a</t>
   </si>
   <si>
     <t>b1==b</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3=</t>
   </si>
 </sst>
 </file>
@@ -471,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871B0360-4A65-8D4C-9F92-BAB28DCD4F5A}">
-  <dimension ref="B9:F18"/>
+  <dimension ref="B9:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
@@ -492,54 +474,58 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="0" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
+      <c r="F11"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="0" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B13" s="0"/>
-      <c r="C13" s="0"/>
-      <c r="D13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>17</v>
+      <c r="B13" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>40.0</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B14" s="0" t="s">
-        <v>0</v>
+      <c r="B14" s="0" t="n">
+        <v>12.0</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.2">
@@ -590,23 +576,6 @@
         <v>0.0</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="n" s="0">
-        <v>12.0</v>
-      </c>
-      <c r="C18" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D18" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E18" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F18" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>

--- a/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
+++ b/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="13">
   <si>
     <t>a</t>
   </si>
@@ -453,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871B0360-4A65-8D4C-9F92-BAB28DCD4F5A}">
-  <dimension ref="B9:F17"/>
+  <dimension ref="B9:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
@@ -481,7 +481,7 @@
       </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11"/>
+      <c r="F11" s="0"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="0" t="s">
@@ -579,6 +579,15 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
+++ b/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekosolapova/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekosolapova/.openl/user-workspace/ekosolapova/BugReproducing2-DEFAULT-2026-07-31_07-55-00/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA127AA8-D6A8-4B44-85F0-61ACA209C8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4F5697-C2D2-0F48-9447-CF690F6C4B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41920" yWindow="5860" windowWidth="28040" windowHeight="17180" xr2:uid="{E3DE3929-4317-194E-8739-045E2F8BD10D}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" xr2:uid="{E3DE3929-4317-194E-8739-045E2F8BD10D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,35 +39,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>a</t>
   </si>
   <si>
-    <t>Rules Double bla( Integer a, Integer b)</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
-    <t>CH1</t>
-  </si>
-  <si>
     <t>RET1</t>
   </si>
   <si>
-    <t>Integer a</t>
-  </si>
-  <si>
-    <t>Integer b</t>
-  </si>
-  <si>
     <t>HC1</t>
   </si>
   <si>
-    <t>a1</t>
-  </si>
-  <si>
     <t>Integer a1</t>
   </si>
   <si>
@@ -78,6 +63,61 @@
   </si>
   <si>
     <t>b1==b</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>c==c1</t>
+  </si>
+  <si>
+    <t>Integer c1</t>
+  </si>
+  <si>
+    <t>Rules Double bla( Integer a, Integer b, Integer c)</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Rules Double BankLimitIndex (Bank bank, RatingGroup bankRatingGroup)</t>
+  </si>
+  <si>
+    <t>bankRatingGroup</t>
+  </si>
+  <si>
+    <t>RatingGroup[]</t>
+  </si>
+  <si>
+    <t>Bank Rating Group /
+Country, Financial Data</t>
+  </si>
+  <si>
+    <t>RU, UA, KZ</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>String[]</t>
+  </si>
+  <si>
+    <t>Rules Double BankLimitIndex (String bank, RatingGroup bankRatingGroup)</t>
+  </si>
+  <si>
+    <t>Rules Double BankLimitIndex (String bank, String bankRatingGroup)</t>
   </si>
 </sst>
 </file>
@@ -85,24 +125,75 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
-      <color theme="1" rgb="000000"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4A452A"/>
+      <name val="Palatino Linotype"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Palatino Linotype"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Palatino Linotype"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C3"/>
+        <bgColor rgb="FFD7E4BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFEEECE1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF376092"/>
+        <bgColor rgb="FF1F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9CDE5"/>
+        <bgColor rgb="FFC6D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3D69B"/>
+        <bgColor rgb="FFD7E4BD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -110,15 +201,388 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC4BD97"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC4BD97"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC4BD97"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,142 +917,362 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871B0360-4A65-8D4C-9F92-BAB28DCD4F5A}">
-  <dimension ref="B9:F27"/>
+  <dimension ref="B9:I30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B9" t="s" s="0">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B10" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B10" t="s" s="0">
+      <c r="D10" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C10" t="s" s="0">
+      <c r="G10" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B11" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D10" t="s" s="0">
+      <c r="E11" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="0" t="s">
+      <c r="D12" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B13" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="22">
+        <v>10</v>
+      </c>
+      <c r="E13" s="22">
+        <v>20</v>
+      </c>
+      <c r="F13" s="23">
+        <v>30</v>
+      </c>
+      <c r="G13" s="23">
+        <v>34</v>
+      </c>
+      <c r="H13" s="22">
+        <v>42</v>
+      </c>
+      <c r="I13" s="22">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="22">
+        <v>1</v>
+      </c>
+      <c r="C14" s="22">
         <v>12</v>
       </c>
-      <c r="D11" s="0"/>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B12" s="0" t="s">
+      <c r="D14" s="22">
+        <v>1</v>
+      </c>
+      <c r="E14" s="22">
+        <v>0</v>
+      </c>
+      <c r="F14" s="22">
+        <v>0</v>
+      </c>
+      <c r="G14" s="22">
+        <v>0</v>
+      </c>
+      <c r="H14" s="22">
+        <v>2</v>
+      </c>
+      <c r="I14" s="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B15" s="22">
+        <v>2</v>
+      </c>
+      <c r="C15" s="24">
+        <v>13</v>
+      </c>
+      <c r="D15" s="22">
+        <v>2</v>
+      </c>
+      <c r="E15" s="22">
+        <v>0</v>
+      </c>
+      <c r="F15" s="22">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22">
+        <v>0</v>
+      </c>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="22">
+        <v>3</v>
+      </c>
+      <c r="C16" s="24"/>
+      <c r="D16" s="22">
+        <v>3</v>
+      </c>
+      <c r="E16" s="22">
+        <v>0</v>
+      </c>
+      <c r="F16" s="22">
+        <v>0</v>
+      </c>
+      <c r="G16" s="22">
+        <v>0</v>
+      </c>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" s="22">
+        <v>4</v>
+      </c>
+      <c r="C17" s="24"/>
+      <c r="D17" s="22">
+        <v>4</v>
+      </c>
+      <c r="E17" s="22">
+        <v>3</v>
+      </c>
+      <c r="F17" s="22">
+        <v>4</v>
+      </c>
+      <c r="G17" s="22">
+        <v>4</v>
+      </c>
+      <c r="H17" s="22">
+        <v>4</v>
+      </c>
+      <c r="I17" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B24" s="5"/>
+      <c r="C24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="8"/>
+      <c r="C25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="2:9" ht="121" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="11"/>
+      <c r="C26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="15"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B27" s="16">
+        <v>7</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="18">
+        <v>1</v>
+      </c>
+      <c r="E27" s="18">
+        <v>0.25</v>
+      </c>
+      <c r="F27" s="18">
+        <v>0.8</v>
+      </c>
+      <c r="G27" s="18">
+        <v>1</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B28" s="16">
+        <v>8</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="18">
+        <v>0.9</v>
+      </c>
+      <c r="E28" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="F28" s="18">
+        <v>0.7</v>
+      </c>
+      <c r="G28" s="18">
+        <v>1</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="16">
         <v>9</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C29" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="18">
+        <v>0.7</v>
+      </c>
+      <c r="E29" s="18">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F29" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="G29" s="18">
+        <v>0.9</v>
+      </c>
+      <c r="H29" s="19">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B30" s="16">
         <v>10</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B13" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="E13" s="0" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B14" s="0" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E14" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B15" s="0" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B16" s="0" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E16" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F16" s="0" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="n" s="0">
-        <v>12.0</v>
-      </c>
-      <c r="C17" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D17" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="E17" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F17" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
+      <c r="C30" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="18">
+        <v>0.25</v>
+      </c>
+      <c r="E30" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="F30" s="18">
+        <v>0.25</v>
+      </c>
+      <c r="G30" s="18">
+        <v>0.7</v>
+      </c>
+      <c r="H30" s="19">
+        <v>0.02</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
+++ b/BugReproducing2-DEFAULT-2026-07-31_07-55-00/BugReproducing (1).xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
   <si>
     <t>a</t>
   </si>
@@ -917,203 +917,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871B0360-4A65-8D4C-9F92-BAB28DCD4F5A}">
-  <dimension ref="B9:I30"/>
+  <dimension ref="B9:H40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="26"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="22">
-        <v>10</v>
-      </c>
-      <c r="E13" s="22">
-        <v>20</v>
-      </c>
-      <c r="F13" s="23">
-        <v>30</v>
-      </c>
-      <c r="G13" s="23">
-        <v>34</v>
-      </c>
-      <c r="H13" s="22">
-        <v>42</v>
-      </c>
-      <c r="I13" s="22">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="22">
-        <v>1</v>
-      </c>
-      <c r="C14" s="22">
-        <v>12</v>
-      </c>
-      <c r="D14" s="22">
-        <v>1</v>
-      </c>
-      <c r="E14" s="22">
-        <v>0</v>
-      </c>
-      <c r="F14" s="22">
-        <v>0</v>
-      </c>
-      <c r="G14" s="22">
-        <v>0</v>
-      </c>
-      <c r="H14" s="22">
-        <v>2</v>
-      </c>
-      <c r="I14" s="22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B15" s="22">
-        <v>2</v>
-      </c>
-      <c r="C15" s="24">
-        <v>13</v>
-      </c>
-      <c r="D15" s="22">
-        <v>2</v>
-      </c>
-      <c r="E15" s="22">
-        <v>0</v>
-      </c>
-      <c r="F15" s="22">
-        <v>0</v>
-      </c>
-      <c r="G15" s="22">
-        <v>0</v>
-      </c>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B16" s="22">
-        <v>3</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="22">
-        <v>3</v>
-      </c>
-      <c r="E16" s="22">
-        <v>0</v>
-      </c>
-      <c r="F16" s="22">
-        <v>0</v>
-      </c>
-      <c r="G16" s="22">
-        <v>0</v>
-      </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="22">
-        <v>4</v>
-      </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="22">
-        <v>4</v>
-      </c>
-      <c r="E17" s="22">
-        <v>3</v>
-      </c>
-      <c r="F17" s="22">
-        <v>4</v>
-      </c>
-      <c r="G17" s="22">
-        <v>4</v>
-      </c>
-      <c r="H17" s="22">
-        <v>4</v>
-      </c>
-      <c r="I17" s="22">
-        <v>4</v>
-      </c>
-    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2"/>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>25</v>
@@ -1267,12 +1082,16 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>